--- a/model-statistics/Model_list.xlsx
+++ b/model-statistics/Model_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucille/Desktop/Gerya_plume/sta/model-statistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45587CBE-AFDC-7D4C-A846-6D20AC468571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76073B10-CD70-AA48-A93A-FC09B9EED2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="1820" windowWidth="27640" windowHeight="15620" xr2:uid="{9DFA58F6-8CD5-FF4A-9280-C9364267072B}"/>
+    <workbookView xWindow="1160" yWindow="980" windowWidth="27640" windowHeight="15620" xr2:uid="{9DFA58F6-8CD5-FF4A-9280-C9364267072B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="59">
   <si>
     <t>Name</t>
   </si>
@@ -192,6 +192,27 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>model-8-21</t>
+  </si>
+  <si>
+    <t>model-8-22</t>
+  </si>
+  <si>
+    <t>250-150 km TBL</t>
+  </si>
+  <si>
+    <t>model-8-23</t>
+  </si>
+  <si>
+    <t>higher resolution</t>
+  </si>
+  <si>
+    <t>model-8-24</t>
+  </si>
+  <si>
+    <t>350-250 km TBL</t>
   </si>
 </sst>
 </file>
@@ -263,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -275,12 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,13 +631,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3694F8-B903-E143-8A2D-D65217FD3A4A}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -640,8 +656,9 @@
       <c r="F1" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -661,7 +678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -681,7 +698,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -701,7 +718,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -721,7 +738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -741,7 +758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -761,7 +778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -781,7 +798,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -801,7 +818,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -821,7 +838,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -841,7 +858,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -861,7 +878,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -881,7 +898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -901,7 +918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -921,7 +938,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -941,7 +958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -961,7 +978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -981,7 +998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1001,7 +1018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
@@ -1021,7 +1038,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1041,109 +1058,118 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1">
-        <v>150</v>
-      </c>
-      <c r="C22" s="1">
-        <v>450</v>
-      </c>
-      <c r="D22" s="1">
-        <v>120</v>
-      </c>
-      <c r="E22" s="1">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22">
+        <v>150</v>
+      </c>
+      <c r="C22">
+        <v>450</v>
+      </c>
+      <c r="D22">
+        <v>120</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="F22" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>150</v>
+      </c>
+      <c r="C23">
+        <v>450</v>
+      </c>
+      <c r="D23">
+        <v>120</v>
+      </c>
+      <c r="E23">
+        <v>15</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24">
+        <v>150</v>
+      </c>
+      <c r="C24">
+        <v>450</v>
+      </c>
+      <c r="D24">
+        <v>120</v>
+      </c>
+      <c r="E24">
+        <v>15</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="1">
+        <v>150</v>
+      </c>
+      <c r="C25" s="1">
+        <v>450</v>
+      </c>
+      <c r="D25" s="1">
+        <v>120</v>
+      </c>
+      <c r="E25" s="1">
+        <v>15</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>25</v>
-      </c>
-      <c r="B25">
-        <v>150</v>
-      </c>
-      <c r="C25">
-        <v>650</v>
-      </c>
-      <c r="D25">
-        <v>90</v>
-      </c>
-      <c r="E25">
-        <v>25</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>150</v>
-      </c>
-      <c r="C26">
-        <v>650</v>
-      </c>
-      <c r="D26">
-        <v>90</v>
-      </c>
-      <c r="E26">
-        <v>20</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>150</v>
-      </c>
-      <c r="C27">
-        <v>650</v>
-      </c>
-      <c r="D27">
-        <v>90</v>
-      </c>
-      <c r="E27">
-        <v>15</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>28</v>
       </c>
       <c r="B28">
         <v>150</v>
@@ -1155,15 +1181,15 @@
         <v>90</v>
       </c>
       <c r="E28">
-        <v>10</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>150</v>
@@ -1175,75 +1201,75 @@
         <v>90</v>
       </c>
       <c r="E29">
+        <v>20</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>150</v>
+      </c>
+      <c r="C30">
+        <v>650</v>
+      </c>
+      <c r="D30">
+        <v>90</v>
+      </c>
+      <c r="E30">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>150</v>
+      </c>
+      <c r="C31">
+        <v>650</v>
+      </c>
+      <c r="D31">
+        <v>90</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>150</v>
+      </c>
+      <c r="C32">
+        <v>650</v>
+      </c>
+      <c r="D32">
+        <v>90</v>
+      </c>
+      <c r="E32">
         <v>5</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>150</v>
-      </c>
-      <c r="C30">
-        <v>550</v>
-      </c>
-      <c r="D30">
-        <v>90</v>
-      </c>
-      <c r="E30">
-        <v>25</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>150</v>
-      </c>
-      <c r="C31">
-        <v>550</v>
-      </c>
-      <c r="D31">
-        <v>90</v>
-      </c>
-      <c r="E31">
-        <v>20</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>150</v>
-      </c>
-      <c r="C32">
-        <v>550</v>
-      </c>
-      <c r="D32">
-        <v>90</v>
-      </c>
-      <c r="E32">
-        <v>15</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>150</v>
@@ -1255,15 +1281,15 @@
         <v>90</v>
       </c>
       <c r="E33">
-        <v>10</v>
-      </c>
-      <c r="F33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34">
         <v>150</v>
@@ -1275,21 +1301,21 @@
         <v>90</v>
       </c>
       <c r="E34">
-        <v>5</v>
-      </c>
-      <c r="F34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B35">
         <v>150</v>
       </c>
       <c r="C35">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="D35">
         <v>90</v>
@@ -1297,53 +1323,53 @@
       <c r="E35">
         <v>15</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B36">
         <v>150</v>
       </c>
       <c r="C36">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="D36">
         <v>90</v>
       </c>
       <c r="E36">
-        <v>5</v>
-      </c>
-      <c r="F36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>150</v>
       </c>
       <c r="C37">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="D37">
         <v>90</v>
       </c>
       <c r="E37">
-        <v>25</v>
-      </c>
-      <c r="F37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B38">
         <v>150</v>
@@ -1355,15 +1381,15 @@
         <v>90</v>
       </c>
       <c r="E38">
-        <v>20</v>
-      </c>
-      <c r="F38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39">
         <v>150</v>
@@ -1375,21 +1401,21 @@
         <v>90</v>
       </c>
       <c r="E39">
-        <v>15</v>
-      </c>
-      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40">
         <v>150</v>
       </c>
       <c r="C40">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="D40">
         <v>90</v>
@@ -1397,19 +1423,19 @@
       <c r="E40">
         <v>25</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B41">
         <v>150</v>
       </c>
       <c r="C41">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="D41">
         <v>90</v>
@@ -1417,19 +1443,19 @@
       <c r="E41">
         <v>20</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>150</v>
       </c>
       <c r="C42">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="D42">
         <v>90</v>
@@ -1437,13 +1463,13 @@
       <c r="E42">
         <v>15</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B43">
         <v>150</v>
@@ -1455,15 +1481,15 @@
         <v>90</v>
       </c>
       <c r="E43">
-        <v>10</v>
-      </c>
-      <c r="F43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B44">
         <v>150</v>
@@ -1475,21 +1501,21 @@
         <v>90</v>
       </c>
       <c r="E44">
-        <v>5</v>
-      </c>
-      <c r="F44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>150</v>
       </c>
       <c r="C45">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="D45">
         <v>90</v>
@@ -1497,67 +1523,127 @@
       <c r="E45">
         <v>15</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>51</v>
+      <c r="F45" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46">
         <v>150</v>
       </c>
       <c r="C46">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="D46">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E46">
-        <v>15</v>
-      </c>
-      <c r="F46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>150</v>
+      </c>
+      <c r="C47">
+        <v>350</v>
+      </c>
+      <c r="D47">
+        <v>90</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48">
+        <v>150</v>
+      </c>
+      <c r="C48">
+        <v>450</v>
+      </c>
+      <c r="D48">
+        <v>90</v>
+      </c>
+      <c r="E48">
+        <v>15</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49">
+        <v>150</v>
+      </c>
+      <c r="C49">
+        <v>450</v>
+      </c>
+      <c r="D49">
+        <v>180</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>46</v>
       </c>
-      <c r="B47">
-        <v>150</v>
-      </c>
-      <c r="C47">
-        <v>450</v>
-      </c>
-      <c r="D47">
-        <v>150</v>
-      </c>
-      <c r="E47">
+      <c r="B50">
+        <v>150</v>
+      </c>
+      <c r="C50">
+        <v>450</v>
+      </c>
+      <c r="D50">
+        <v>150</v>
+      </c>
+      <c r="E50">
         <v>15</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="F50" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="1">
-        <v>150</v>
-      </c>
-      <c r="C48" s="1">
-        <v>450</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="B51" s="1">
+        <v>150</v>
+      </c>
+      <c r="C51" s="1">
+        <v>450</v>
+      </c>
+      <c r="D51" s="1">
         <v>60</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E51" s="1">
         <v>15</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F51" s="6" t="s">
         <v>50</v>
       </c>
     </row>
